--- a/data/trans_camb/P1412-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1412-Clase-trans_camb.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,72</t>
+          <t>0,22; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,6</t>
+          <t>0,59; 2,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,93</t>
+          <t>-1,26; 0,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,03</t>
+          <t>-0,42; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,47</t>
+          <t>0,1; 1,41</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>262,49%</t>
+          <t>264,34%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-90,39; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,3; —</t>
+          <t>-32,01; —</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,46; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,11</t>
+          <t>-0,5; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,77; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,65</t>
+          <t>-0,21; 0,67</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>115,17%</t>
+          <t>117,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>160,6%</t>
+          <t>155,21%</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,6</t>
+          <t>-1,55; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,13</t>
+          <t>-0,89; 1,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,53</t>
+          <t>-1,07; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,97</t>
+          <t>-0,5; 1,38</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 423,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-85,7; 323,81</t>
+          <t>-70,14; 639,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 299,33</t>
+          <t>-100,0; 439,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,48; 375,43</t>
+          <t>-65,31; 680,9</t>
         </is>
       </c>
     </row>
@@ -1066,27 +1066,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,17</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,86</t>
+          <t>-0,95; 0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,89</t>
+          <t>-0,75; 0,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,78</t>
+          <t>-0,23; 0,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,77</t>
+          <t>0,01; 1,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,56</t>
+          <t>-0,52; 0,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,55</t>
+          <t>-0,32; 0,68</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235,64%</t>
+          <t>357,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 157,22</t>
+          <t>-61,88; 118,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,24; 146,6</t>
+          <t>-55,34; 151,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 130,63</t>
+          <t>-55,33; 120,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 112,67</t>
+          <t>-37,82; 148,38</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,57</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,48</t>
+          <t>-0,84; 1,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,89</t>
+          <t>-1,25; 0,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,38</t>
+          <t>-1,74; 0,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; -0,15</t>
+          <t>-1,82; 0,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,49</t>
+          <t>-1,08; 0,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,02</t>
+          <t>-1,39; 0,02</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-10,57%</t>
+          <t>-22,52%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-66,57%</t>
+          <t>-57,7%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-51,59%</t>
+          <t>-47,66%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,44; 487,63</t>
+          <t>-62,99; 661,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,61; 381,99</t>
+          <t>-84,62; 316,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,77; 61,89</t>
+          <t>-88,05; 53,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-87,01; -8,01</t>
+          <t>-83,17; 10,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 71,3</t>
+          <t>-63,32; 81,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,54; 5,69</t>
+          <t>-76,51; 6,04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,92</t>
+          <t>-0,79; 0,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,33</t>
+          <t>-1,15; 0,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,71</t>
+          <t>-0,63; 0,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,23</t>
+          <t>-0,84; 0,3</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-35,06%</t>
+          <t>-32,05%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-38,78%</t>
+          <t>-34,2%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 170,49</t>
+          <t>-59,85; 178,5</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 82,36</t>
+          <t>-76,59; 60,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 163,79</t>
+          <t>-57,25; 220,62</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,85; 60,18</t>
+          <t>-73,87; 92,42</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,05</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,5</t>
+          <t>-0,28; 0,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,63</t>
+          <t>-0,15; 0,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,22</t>
+          <t>-0,53; 0,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,09</t>
+          <t>-0,5; 0,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,27</t>
+          <t>-0,32; 0,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,25</t>
+          <t>-0,21; 0,33</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-30,77%</t>
+          <t>-20,09%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,81%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 101,01</t>
+          <t>-33,82; 115,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 136,91</t>
+          <t>-19,39; 143,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,52; 48,53</t>
+          <t>-59,56; 53,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 21,4</t>
+          <t>-50,65; 36,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 51,45</t>
+          <t>-38,79; 44,58</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 47,08</t>
+          <t>-25,4; 61,78</t>
         </is>
       </c>
     </row>
